--- a/data/obx_xlsx/ODF.OL.xlsx
+++ b/data/obx_xlsx/ODF.OL.xlsx
@@ -10721,12 +10721,30 @@
       <c r="Q33" s="16">
         <v>623.2</v>
       </c>
-      <c r="R33" s="15"/>
-      <c r="S33" s="15"/>
-      <c r="T33" s="15"/>
-      <c r="U33" s="15"/>
-      <c r="V33" s="15"/>
-      <c r="W33" s="15"/>
+      <c r="R33" s="15">
+        <f t="shared" ref="R33:W33" si="1">SUM(R34:R37)</f>
+        <v>597.7</v>
+      </c>
+      <c r="S33" s="15">
+        <f t="shared" si="1"/>
+        <v>724.14</v>
+      </c>
+      <c r="T33" s="15">
+        <f t="shared" si="1"/>
+        <v>532.31</v>
+      </c>
+      <c r="U33" s="15">
+        <f t="shared" si="1"/>
+        <v>1030.2</v>
+      </c>
+      <c r="V33" s="15">
+        <f t="shared" si="1"/>
+        <v>733.96</v>
+      </c>
+      <c r="W33" s="15">
+        <f t="shared" si="1"/>
+        <v>782.97</v>
+      </c>
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="14" t="s">
